--- a/Circuit/部品リスト.xlsx
+++ b/Circuit/部品リスト.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/banbatakumi/GitHub/Sci-Tech/Circuit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AAB20A82-6BAE-B043-842E-57D9558E9C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999941D0-30BF-FF43-BEAA-D9A72BD6CBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26060" yWindow="600" windowWidth="25140" windowHeight="28200" xr2:uid="{09AFFD13-22AC-6A45-8616-800B7A426BDB}"/>
+    <workbookView xWindow="26060" yWindow="600" windowWidth="25140" windowHeight="28200" activeTab="1" xr2:uid="{09AFFD13-22AC-6A45-8616-800B7A426BDB}"/>
   </bookViews>
   <sheets>
     <sheet name="メイン基板" sheetId="1" r:id="rId1"/>
     <sheet name="モータードライバ" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -710,7 +710,7 @@
         <v>700</v>
       </c>
       <c r="F2">
-        <f>D2*E2</f>
+        <f t="shared" ref="F2:F19" si="0">D2*E2</f>
         <v>700</v>
       </c>
     </row>
@@ -731,7 +731,7 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <f>D3*E3</f>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
@@ -752,7 +752,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <f>D4*E4</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -773,7 +773,7 @@
         <v>30</v>
       </c>
       <c r="F5">
-        <f>D5*E5</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
@@ -794,7 +794,7 @@
         <v>30</v>
       </c>
       <c r="F6">
-        <f>D6*E6</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
@@ -815,7 +815,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <f>D7*E7</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
@@ -836,7 +836,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <f>D8*E8</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
@@ -857,7 +857,7 @@
         <v>27.5</v>
       </c>
       <c r="F9">
-        <f>D9*E9</f>
+        <f t="shared" si="0"/>
         <v>27.5</v>
       </c>
     </row>
@@ -878,7 +878,7 @@
         <v>80</v>
       </c>
       <c r="F10">
-        <f>D10*E10</f>
+        <f t="shared" si="0"/>
         <v>160</v>
       </c>
     </row>
@@ -899,7 +899,7 @@
         <v>15</v>
       </c>
       <c r="F11">
-        <f>D11*E11</f>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
     </row>
@@ -920,7 +920,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <f>D12*E12</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
@@ -941,7 +941,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <f>D13*E13</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
@@ -962,7 +962,7 @@
         <v>1.5</v>
       </c>
       <c r="F14">
-        <f>D14*E14</f>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
     </row>
@@ -983,7 +983,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <f>D15*E15</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
         <v>5</v>
       </c>
       <c r="F16">
-        <f>D16*E16</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
         <v>5</v>
       </c>
       <c r="F17">
-        <f>D17*E17</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <f>D18*E18</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <f>D19*E19</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <f t="shared" ref="F20:F26" si="0">D20*E20</f>
+        <f t="shared" ref="F20:F26" si="1">D20*E20</f>
         <v>50</v>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
         <v>20</v>
       </c>
       <c r="F21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         <v>30</v>
       </c>
       <c r="F22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -1187,14 +1187,14 @@
         <v>111637</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25">
         <v>10</v>
       </c>
       <c r="F25">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1214,14 +1214,14 @@
         <v>25</v>
       </c>
       <c r="F26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="F27">
         <f>SUM(F2:F26)</f>
-        <v>1752.5</v>
+        <v>1762.5</v>
       </c>
     </row>
   </sheetData>
